--- a/results/job_matches_2026-07-20.xlsx
+++ b/results/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0162590b4bca3d10</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d44fe55ea5358c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0162590b4bca3d10</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90259e539c619c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d44fe55ea5358c0</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3745a4ff718ce48f</t>
+          <t>https://www.indeed.com/viewjob?jk=90259e539c619c3a</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d8e6b9fcebf351</t>
+          <t>https://www.indeed.com/viewjob?jk=3745a4ff718ce48f</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f10acc01735c15</t>
+          <t>https://www.indeed.com/viewjob?jk=22d8e6b9fcebf351</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17631ca9c910c51a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f10acc01735c15</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23567ec8e77ea65b</t>
+          <t>https://www.indeed.com/viewjob?jk=17631ca9c910c51a</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9eef8d0c0765532</t>
+          <t>https://www.indeed.com/viewjob?jk=23567ec8e77ea65b</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7accd1dc6af81c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9eef8d0c0765532</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0deb86a680c0de</t>
+          <t>https://www.indeed.com/viewjob?jk=a7accd1dc6af81c7</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058219ed3cf271c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0deb86a680c0de</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5960061ff2c14124</t>
+          <t>https://www.indeed.com/viewjob?jk=058219ed3cf271c8</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcd71145988051b</t>
+          <t>https://www.indeed.com/viewjob?jk=5960061ff2c14124</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1bb8ce02c165ea</t>
+          <t>https://www.indeed.com/viewjob?jk=efcd71145988051b</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb37d33702c42988</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1bb8ce02c165ea</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8907c281b0e38f47</t>
+          <t>https://www.indeed.com/viewjob?jk=fb37d33702c42988</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebf422d6142215</t>
+          <t>https://www.indeed.com/viewjob?jk=8907c281b0e38f47</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902226c872c65d76</t>
+          <t>https://www.indeed.com/viewjob?jk=beebf422d6142215</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e362ca7c899ed</t>
+          <t>https://www.indeed.com/viewjob?jk=902226c872c65d76</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51fccdaf83e7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e362ca7c899ed</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f65723c1b0cc42c</t>
+          <t>https://www.indeed.com/viewjob?jk=b51fccdaf83e7a45</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e1a7479e3c6d75</t>
+          <t>https://www.indeed.com/viewjob?jk=1f65723c1b0cc42c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5cc50e4e4adbf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e1a7479e3c6d75</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc11fd2fdbc68b19</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5cc50e4e4adbf8</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec1122013ede43c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc11fd2fdbc68b19</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b56b67b5618828</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec1122013ede43c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb2d0031f21849e</t>
+          <t>https://www.indeed.com/viewjob?jk=26b56b67b5618828</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3273f104f39f71f</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb2d0031f21849e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4545129fbd8171</t>
+          <t>https://www.indeed.com/viewjob?jk=a3273f104f39f71f</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893ba2b33005a817</t>
+          <t>https://www.indeed.com/viewjob?jk=be4545129fbd8171</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5936c0fe3cc1d810</t>
+          <t>https://www.indeed.com/viewjob?jk=893ba2b33005a817</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde6bd7b18d8094e</t>
+          <t>https://www.indeed.com/viewjob?jk=5936c0fe3cc1d810</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d82d34c4d4d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=bde6bd7b18d8094e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ae845d5455b185</t>
+          <t>https://www.indeed.com/viewjob?jk=93d82d34c4d4d9f9</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3932d8bffff36f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ae845d5455b185</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d933358595b905a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3932d8bffff36f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44af55d588aefe42</t>
+          <t>https://www.indeed.com/viewjob?jk=8d933358595b905a</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32914027e92100b4</t>
+          <t>https://www.indeed.com/viewjob?jk=44af55d588aefe42</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75736eaa5f691233</t>
+          <t>https://www.indeed.com/viewjob?jk=32914027e92100b4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7df172e8ccdf8d</t>
+          <t>https://www.indeed.com/viewjob?jk=75736eaa5f691233</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc9672f510c9438</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7df172e8ccdf8d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91dfbf05e523fa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc9672f510c9438</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b56f3704d5d66e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=91dfbf05e523fa6e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d139d3986b9afd07</t>
+          <t>https://www.indeed.com/viewjob?jk=b56f3704d5d66e0f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c0dc12ce6825fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d139d3986b9afd07</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84bf5bd57711a</t>
+          <t>https://www.indeed.com/viewjob?jk=94c0dc12ce6825fd</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef90d605a9f8edf</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84bf5bd57711a</t>
         </is>
       </c>
     </row>
@@ -2158,23 +2158,58 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ef90d605a9f8edf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>TX, US USA</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fc1ceec59ac88d89</t>
         </is>

--- a/results/job_matches_2026-07-20.xlsx
+++ b/results/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0162590b4bca3d10</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Neomax</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d44fe55ea5358c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0162590b4bca3d10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90259e539c619c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3745a4ff718ce48f</t>
+          <t>https://www.indeed.com/viewjob?jk=1d44fe55ea5358c0</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d8e6b9fcebf351</t>
+          <t>https://www.indeed.com/viewjob?jk=90259e539c619c3a</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f10acc01735c15</t>
+          <t>https://www.indeed.com/viewjob?jk=3745a4ff718ce48f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17631ca9c910c51a</t>
+          <t>https://www.indeed.com/viewjob?jk=22d8e6b9fcebf351</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23567ec8e77ea65b</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f10acc01735c15</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9eef8d0c0765532</t>
+          <t>https://www.indeed.com/viewjob?jk=17631ca9c910c51a</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7accd1dc6af81c7</t>
+          <t>https://www.indeed.com/viewjob?jk=23567ec8e77ea65b</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0deb86a680c0de</t>
+          <t>https://www.indeed.com/viewjob?jk=c9eef8d0c0765532</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058219ed3cf271c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a7accd1dc6af81c7</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5960061ff2c14124</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0deb86a680c0de</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcd71145988051b</t>
+          <t>https://www.indeed.com/viewjob?jk=058219ed3cf271c8</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1bb8ce02c165ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5960061ff2c14124</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb37d33702c42988</t>
+          <t>https://www.indeed.com/viewjob?jk=efcd71145988051b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8907c281b0e38f47</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1bb8ce02c165ea</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebf422d6142215</t>
+          <t>https://www.indeed.com/viewjob?jk=fb37d33702c42988</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902226c872c65d76</t>
+          <t>https://www.indeed.com/viewjob?jk=8907c281b0e38f47</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e362ca7c899ed</t>
+          <t>https://www.indeed.com/viewjob?jk=beebf422d6142215</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51fccdaf83e7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=902226c872c65d76</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f65723c1b0cc42c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e362ca7c899ed</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e1a7479e3c6d75</t>
+          <t>https://www.indeed.com/viewjob?jk=b51fccdaf83e7a45</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5cc50e4e4adbf8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f65723c1b0cc42c</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc11fd2fdbc68b19</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e1a7479e3c6d75</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec1122013ede43c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5cc50e4e4adbf8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b56b67b5618828</t>
+          <t>https://www.indeed.com/viewjob?jk=bc11fd2fdbc68b19</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb2d0031f21849e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec1122013ede43c</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3273f104f39f71f</t>
+          <t>https://www.indeed.com/viewjob?jk=26b56b67b5618828</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4545129fbd8171</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb2d0031f21849e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893ba2b33005a817</t>
+          <t>https://www.indeed.com/viewjob?jk=a3273f104f39f71f</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5936c0fe3cc1d810</t>
+          <t>https://www.indeed.com/viewjob?jk=be4545129fbd8171</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde6bd7b18d8094e</t>
+          <t>https://www.indeed.com/viewjob?jk=893ba2b33005a817</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d82d34c4d4d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5936c0fe3cc1d810</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ae845d5455b185</t>
+          <t>https://www.indeed.com/viewjob?jk=bde6bd7b18d8094e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3932d8bffff36f</t>
+          <t>https://www.indeed.com/viewjob?jk=93d82d34c4d4d9f9</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d933358595b905a</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ae845d5455b185</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44af55d588aefe42</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3932d8bffff36f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32914027e92100b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d933358595b905a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75736eaa5f691233</t>
+          <t>https://www.indeed.com/viewjob?jk=44af55d588aefe42</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7df172e8ccdf8d</t>
+          <t>https://www.indeed.com/viewjob?jk=32914027e92100b4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc9672f510c9438</t>
+          <t>https://www.indeed.com/viewjob?jk=75736eaa5f691233</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91dfbf05e523fa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7df172e8ccdf8d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b56f3704d5d66e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc9672f510c9438</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d139d3986b9afd07</t>
+          <t>https://www.indeed.com/viewjob?jk=91dfbf05e523fa6e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c0dc12ce6825fd</t>
+          <t>https://www.indeed.com/viewjob?jk=b56f3704d5d66e0f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84bf5bd57711a</t>
+          <t>https://www.indeed.com/viewjob?jk=d139d3986b9afd07</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef90d605a9f8edf</t>
+          <t>https://www.indeed.com/viewjob?jk=94c0dc12ce6825fd</t>
         </is>
       </c>
     </row>
@@ -2193,23 +2193,93 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa84bf5bd57711a</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ef90d605a9f8edf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>TX, US USA</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fc1ceec59ac88d89</t>
         </is>

--- a/results/job_matches_2026-07-20.xlsx
+++ b/results/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,17 +626,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d44fe55ea5358c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90259e539c619c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d44fe55ea5358c0</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3745a4ff718ce48f</t>
+          <t>https://www.indeed.com/viewjob?jk=90259e539c619c3a</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d8e6b9fcebf351</t>
+          <t>https://www.indeed.com/viewjob?jk=3745a4ff718ce48f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f10acc01735c15</t>
+          <t>https://www.indeed.com/viewjob?jk=22d8e6b9fcebf351</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17631ca9c910c51a</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f10acc01735c15</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23567ec8e77ea65b</t>
+          <t>https://www.indeed.com/viewjob?jk=17631ca9c910c51a</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9eef8d0c0765532</t>
+          <t>https://www.indeed.com/viewjob?jk=23567ec8e77ea65b</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7accd1dc6af81c7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9eef8d0c0765532</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0deb86a680c0de</t>
+          <t>https://www.indeed.com/viewjob?jk=a7accd1dc6af81c7</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058219ed3cf271c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0deb86a680c0de</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5960061ff2c14124</t>
+          <t>https://www.indeed.com/viewjob?jk=058219ed3cf271c8</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efcd71145988051b</t>
+          <t>https://www.indeed.com/viewjob?jk=5960061ff2c14124</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1bb8ce02c165ea</t>
+          <t>https://www.indeed.com/viewjob?jk=efcd71145988051b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb37d33702c42988</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1bb8ce02c165ea</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8907c281b0e38f47</t>
+          <t>https://www.indeed.com/viewjob?jk=fb37d33702c42988</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beebf422d6142215</t>
+          <t>https://www.indeed.com/viewjob?jk=8907c281b0e38f47</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902226c872c65d76</t>
+          <t>https://www.indeed.com/viewjob?jk=beebf422d6142215</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f9e362ca7c899ed</t>
+          <t>https://www.indeed.com/viewjob?jk=902226c872c65d76</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51fccdaf83e7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=6f9e362ca7c899ed</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f65723c1b0cc42c</t>
+          <t>https://www.indeed.com/viewjob?jk=b51fccdaf83e7a45</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e1a7479e3c6d75</t>
+          <t>https://www.indeed.com/viewjob?jk=1f65723c1b0cc42c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e5cc50e4e4adbf8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4e1a7479e3c6d75</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc11fd2fdbc68b19</t>
+          <t>https://www.indeed.com/viewjob?jk=3e5cc50e4e4adbf8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec1122013ede43c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc11fd2fdbc68b19</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b56b67b5618828</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec1122013ede43c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfb2d0031f21849e</t>
+          <t>https://www.indeed.com/viewjob?jk=26b56b67b5618828</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3273f104f39f71f</t>
+          <t>https://www.indeed.com/viewjob?jk=cfb2d0031f21849e</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4545129fbd8171</t>
+          <t>https://www.indeed.com/viewjob?jk=a3273f104f39f71f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893ba2b33005a817</t>
+          <t>https://www.indeed.com/viewjob?jk=be4545129fbd8171</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5936c0fe3cc1d810</t>
+          <t>https://www.indeed.com/viewjob?jk=893ba2b33005a817</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde6bd7b18d8094e</t>
+          <t>https://www.indeed.com/viewjob?jk=5936c0fe3cc1d810</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d82d34c4d4d9f9</t>
+          <t>https://www.indeed.com/viewjob?jk=bde6bd7b18d8094e</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ae845d5455b185</t>
+          <t>https://www.indeed.com/viewjob?jk=93d82d34c4d4d9f9</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3932d8bffff36f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ae845d5455b185</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d933358595b905a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3932d8bffff36f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44af55d588aefe42</t>
+          <t>https://www.indeed.com/viewjob?jk=8d933358595b905a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32914027e92100b4</t>
+          <t>https://www.indeed.com/viewjob?jk=44af55d588aefe42</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75736eaa5f691233</t>
+          <t>https://www.indeed.com/viewjob?jk=32914027e92100b4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c7df172e8ccdf8d</t>
+          <t>https://www.indeed.com/viewjob?jk=75736eaa5f691233</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc9672f510c9438</t>
+          <t>https://www.indeed.com/viewjob?jk=5c7df172e8ccdf8d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91dfbf05e523fa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc9672f510c9438</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b56f3704d5d66e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=91dfbf05e523fa6e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d139d3986b9afd07</t>
+          <t>https://www.indeed.com/viewjob?jk=b56f3704d5d66e0f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c0dc12ce6825fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d139d3986b9afd07</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa84bf5bd57711a</t>
+          <t>https://www.indeed.com/viewjob?jk=94c0dc12ce6825fd</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ef90d605a9f8edf</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa84bf5bd57711a</t>
         </is>
       </c>
     </row>
@@ -2263,23 +2263,58 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ef90d605a9f8edf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>TX, US USA</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fc1ceec59ac88d89</t>
         </is>

--- a/results/job_matches_2026-07-20.xlsx
+++ b/results/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf053b4e78a7784</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
+          <t>Data Architect (Azure + Databricks)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Nine Core Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,112 +531,2282 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Quantitative Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0162590b4bca3d10</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Data Engineer - ITS4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>State of Minnesota - Minnesota IT Services</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nProspect</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LogicMonitor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Windows Engineer (Expert)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BAE Systems USA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Neomax</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0162590b4bca3d10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Streaming</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Okemos, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Long Key, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hope Hull, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hot Springs Village, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pawtucket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Kennesaw, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Montpelier, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Augusta, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Middletown, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Fremont, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Kansas City, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b3fc91f2cea0cff</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Upper Darby, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b42319358e9825d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0828e77c3d7d3252</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>New Franken, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd855d8b7037bf65</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Charleston, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=915279c42616c491</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a05cfa47b40187d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d907377ff091f914</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0b9571cfd096f5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d19f7de148c2aba2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Corrales, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fc1f317e66777dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3c20343bdf459df</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ea44a5cf8a55d70</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d8c4bfc649925e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>American Red Cross</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Backend Systems</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Qureos</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Louisville, KY, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D67" t="n">
         <v>10.4</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Oracle, Jenkins, Terraform, Jenkins, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69fdb765742c8dbb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-20.xlsx
+++ b/results/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Quantitative Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aktra Inc</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
+          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Data Architect (Azure + Databricks)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Nine Core Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
+          <t>Senior Quantitative Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0162590b4bca3d10</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>SAP FICO Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>GeekSoft Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7242710483aaa20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
+          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>FEED THE CHILDREN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Software Engineer II - Streaming</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Windows Engineer (Expert)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
+          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
+          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
+          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
+          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
+          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
+          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
+          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
+          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
+          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
+          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
+          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
+          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
+          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
+          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
+          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3fc91f2cea0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b42319358e9825d</t>
+          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0828e77c3d7d3252</t>
+          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd855d8b7037bf65</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=915279c42616c491</t>
+          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05cfa47b40187d9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d907377ff091f914</t>
+          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b9571cfd096f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19f7de148c2aba2</t>
+          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc1f317e66777dd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c20343bdf459df</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3fc91f2cea0cff</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea44a5cf8a55d70</t>
+          <t>https://www.indeed.com/viewjob?jk=5b42319358e9825d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8c4bfc649925e7</t>
+          <t>https://www.indeed.com/viewjob?jk=0828e77c3d7d3252</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd855d8b7037bf65</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,89 +2596,89 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=915279c42616c491</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=a05cfa47b40187d9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d907377ff091f914</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Red Cross</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b9571cfd096f5e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Backend Systems</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
+          <t>https://www.indeed.com/viewjob?jk=d19f7de148c2aba2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,40 +2771,635 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc1f317e66777dd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3c20343bdf459df</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Remote</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ea44a5cf8a55d70</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d8c4bfc649925e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Agilify</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Systems Engineer I</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M AgriLife Extension</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>College Station, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a99f136d94c9eab9</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Systems Engineer I</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M AgriLife Extension</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>College Station, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b951b068dc32695</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>American Red Cross</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Engineer- Greensboro, NC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Stake Center Locating</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Qureos</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Backend Systems</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>RE/SPEC Inc</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hollstadt Consulting</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VIVA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bf8e77549f4b069</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>Software Engineer II</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>Citizens</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Plano, TX, US USA</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D85" t="n">
         <v>10.4</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>AWS, Lambda, RDS, Scala, Oracle, Jenkins, Terraform, Jenkins, SonarQube, Git</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=69fdb765742c8dbb</t>
         </is>

--- a/results/job_matches_2026-07-20.xlsx
+++ b/results/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cactus Wellhead - Sr. Full Stack Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Cactus Wellhead LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=54c54e6d23a07fa0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
+          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect (Azure + Databricks)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Nine Core Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
+          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Quantitative Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aktra Inc</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
+          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Quantitative Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP FICO Architect</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GeekSoft Consulting</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7242710483aaa20</t>
+          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
+          <t>SAP FICO Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>GeekSoft Consulting</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=f7242710483aaa20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FEED THE CHILDREN</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Operations Engineer, BizTech</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, SQS, RDS, GCP, Scala, Oracle, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=40f9eb2ccac23ae0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>FEED THE CHILDREN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
+          <t>https://www.indeed.com/viewjob?jk=253a6ac52702e640</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Windows Engineer (Expert)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Software Engineer II - Streaming</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
+          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
+          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
+          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
+          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
+          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
+          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
+          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
+          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
+          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
+          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
+          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
+          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
+          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
+          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3fc91f2cea0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b42319358e9825d</t>
+          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0828e77c3d7d3252</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd855d8b7037bf65</t>
+          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=915279c42616c491</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05cfa47b40187d9</t>
+          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d907377ff091f914</t>
+          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b9571cfd096f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19f7de148c2aba2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc1f317e66777dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3fc91f2cea0cff</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c20343bdf459df</t>
+          <t>https://www.indeed.com/viewjob?jk=5b42319358e9825d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea44a5cf8a55d70</t>
+          <t>https://www.indeed.com/viewjob?jk=0828e77c3d7d3252</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8c4bfc649925e7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd855d8b7037bf65</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=915279c42616c491</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=a05cfa47b40187d9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=d907377ff091f914</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b9571cfd096f5e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d19f7de148c2aba2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Systems Engineer I</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Texas A&amp;M AgriLife Extension</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a99f136d94c9eab9</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc1f317e66777dd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Systems Engineer I</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Texas A&amp;M AgriLife Extension</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b951b068dc32695</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c20343bdf459df</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American Red Cross</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea44a5cf8a55d70</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8c4bfc649925e7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Backend Systems</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf8e77549f4b069</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,15 +3391,435 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Systems Engineer I</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M AgriLife Extension</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>College Station, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a99f136d94c9eab9</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Systems Engineer I</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M AgriLife Extension</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>College Station, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b951b068dc32695</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Software Engineer- Greensboro, NC</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Stake Center Locating</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Qureos</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>American Red Cross</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Payments)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Vancouver, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7956002449dfcaf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Payments)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3915e239710ba577</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Backend Systems</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Hollstadt Consulting</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>VIVA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bf8e77549f4b069</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>RE/SPEC Inc</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Oracle, Jenkins, Terraform, Jenkins, SonarQube, Git</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=69fdb765742c8dbb</t>
         </is>

--- a/results/job_matches_2026-07-20.xlsx
+++ b/results/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cactus Wellhead - Sr. Full Stack Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cactus Wellhead LLC</t>
+          <t>megan soft</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Azure, Databricks</t>
+          <t>Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c54e6d23a07fa0</t>
+          <t>https://www.indeed.com/viewjob?jk=74f99ec032c2a050</t>
         </is>
       </c>
     </row>
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
+          <t>https://www.indeed.com/viewjob?jk=278c7726eee6f36f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Quantitative Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aktra Inc</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
+          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>Senior Quantitative Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP FICO Architect</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GeekSoft Consulting</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Data Modeling, ETL, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7242710483aaa20</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Operations Engineer, BizTech</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, GCP, Scala, Oracle, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40f9eb2ccac23ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>SAP FICO Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>GeekSoft Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=f7242710483aaa20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
+          <t>Operations Engineer, BizTech</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
+          <t>AWS, SQS, RDS, GCP, Scala, Oracle, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=40f9eb2ccac23ae0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FEED THE CHILDREN</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253a6ac52702e640</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>FEED THE CHILDREN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Software Engineer II - Streaming</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Windows Engineer (Expert)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Azure DevOps Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
+          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
+          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
+          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
+          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
+          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
+          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
+          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
+          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
+          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
+          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
+          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
+          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
+          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
+          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
+          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
+          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3fc91f2cea0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b42319358e9825d</t>
+          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0828e77c3d7d3252</t>
+          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd855d8b7037bf65</t>
+          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=915279c42616c491</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05cfa47b40187d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3fc91f2cea0cff</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d907377ff091f914</t>
+          <t>https://www.indeed.com/viewjob?jk=5b42319358e9825d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b9571cfd096f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=0828e77c3d7d3252</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19f7de148c2aba2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd855d8b7037bf65</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc1f317e66777dd</t>
+          <t>https://www.indeed.com/viewjob?jk=915279c42616c491</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c20343bdf459df</t>
+          <t>https://www.indeed.com/viewjob?jk=a05cfa47b40187d9</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea44a5cf8a55d70</t>
+          <t>https://www.indeed.com/viewjob?jk=d907377ff091f914</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8c4bfc649925e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b9571cfd096f5e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=d19f7de148c2aba2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc1f317e66777dd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,102 +3296,102 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3c20343bdf459df</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Software Engineer II - Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=6ea44a5cf8a55d70</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>API/Microservices/AWS Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8c4bfc649925e7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Systems Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Texas A&amp;M AgriLife Extension</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a99f136d94c9eab9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Systems Engineer I</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Texas A&amp;M AgriLife Extension</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b951b068dc32695</t>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>American Red Cross</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
+          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7956002449dfcaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3915e239710ba577</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer Backend Systems</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf8e77549f4b069</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
+          <t>Senior Engineer, Corp Solutions</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>RE/SPEC Inc</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,645 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>American Red Cross</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Payments)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Vancouver, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7956002449dfcaf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (Payments)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3915e239710ba577</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer- Greensboro, NC</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Stake Center Locating</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Qureos</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Systems Engineer I</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M AgriLife Extension</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>College Station, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a99f136d94c9eab9</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Systems Engineer I</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M AgriLife Extension</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>College Station, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b951b068dc32695</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Hollstadt Consulting</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VIVA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bf8e77549f4b069</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RE/SPEC Inc</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Backend Systems</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Oracle, Jenkins, Terraform, Jenkins, SonarQube, Git</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=69fdb765742c8dbb</t>
         </is>

--- a/results/job_matches_2026-07-20.xlsx
+++ b/results/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>iSynergy IT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf053b4e78a7784</t>
+          <t>https://www.indeed.com/viewjob?jk=64aa04af21957dc5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>megan soft</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f99ec032c2a050</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf053b4e78a7784</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>megan soft</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=74f99ec032c2a050</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
+          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Azure, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=704b1f0ab6bff192</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect (Azure + Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Nine Core Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Milpitas, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Hive, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278c7726eee6f36f</t>
+          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrossCountry Mortgage, LLC</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, IAM, RDS, Hive, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
+          <t>https://www.indeed.com/viewjob?jk=278c7726eee6f36f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Quantitative Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aktra Inc</t>
+          <t>CrossCountry Mortgage, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
+          <t>https://www.indeed.com/viewjob?jk=26d0c8a6b975fef0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
+          <t>Senior Quantitative Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Reporting Engineer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdfcb7d4f8c3b02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer - HYBRID/NC RESIDENTS ONLY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc9b66f689cbeefb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Reporting Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
+          <t>https://www.indeed.com/viewjob?jk=59ef3d85179316f9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
+          <t>https://www.indeed.com/viewjob?jk=0eff179e948461c2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Salesforce Business Systems Analyst</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
+          <t>https://www.indeed.com/viewjob?jk=22216c34e7397891</t>
         </is>
       </c>
     </row>
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Highmark Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
+          <t>https://www.indeed.com/viewjob?jk=cb817b0533864176</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
+          <t>Salesforce Business Systems Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UNIFY SOLUTIONS INC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7b799aca0d95f271</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SAP FICO Architect</t>
+          <t>Databricks Data Engineer with Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GeekSoft Consulting</t>
+          <t>UNIFY SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7242710483aaa20</t>
+          <t>https://www.indeed.com/viewjob?jk=eb057adb6c59f5ff</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>SAP FICO Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>GeekSoft Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f7242710483aaa20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Operations Engineer, BizTech</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, GCP, Scala, Oracle, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40f9eb2ccac23ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5d5f535a77ad9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Bricks Data Engineer</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bavel systems LLP</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Operations Engineer, BizTech</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, GCP, Scala, Oracle, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=40f9eb2ccac23ae0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Data Bricks Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bavel systems LLP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=2d997e2a6aa4fbed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nProspect</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FEED THE CHILDREN</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>AWS DevOps Engineer Experience in Pega Platform EKS with Jenkins and Terraform DevOps OnlyUS Citizen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>nProspect</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Kafka, Cassandra, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=1c8c651e8e033eb5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>FEED THE CHILDREN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4416990cb07c5b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer II - Streaming</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Data Modeling, ETL, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Windows Engineer (Expert)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c91b09d863e5b13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure DevOps Architect</t>
+          <t>Software Engineer II - Streaming</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Rivian and Volkswagen Group Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Kafka Connect, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
+          <t>Windows Engineer (Expert)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
+          <t>https://www.indeed.com/viewjob?jk=09ee1d1985ee70d9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Azure DevOps Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Glue, IAM, RDS, Azure, GCP, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
+          <t>https://www.indeed.com/viewjob?jk=198e8bee7c6735a3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, Maven</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Full Stack .NET Developer – C#, React, Azure/AWS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
+          <t>https://www.indeed.com/viewjob?jk=ceec9a4f672d1616</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
+          <t>https://www.indeed.com/viewjob?jk=81fbe0e290779fed</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
+          <t>https://www.indeed.com/viewjob?jk=ac311697ccb3853f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab98484eaf838986</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
+          <t>https://www.indeed.com/viewjob?jk=32b88aca77632a92</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b1866a8d72d20f34</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd0c998782c2f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
+          <t>https://www.indeed.com/viewjob?jk=e91d465de09c8700</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
+          <t>https://www.indeed.com/viewjob?jk=dc1fb0b5d2fd9e9a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9297ffdbc46b96</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed020becb4a83e8</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
+          <t>https://www.indeed.com/viewjob?jk=358aea846166503d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
+          <t>https://www.indeed.com/viewjob?jk=52180e5720e83c14</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdacfd27451cfb7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
+          <t>https://www.indeed.com/viewjob?jk=19925dab32bbdb67</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
+          <t>https://www.indeed.com/viewjob?jk=60a409d926368683</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
+          <t>https://www.indeed.com/viewjob?jk=49c4a14f355944b0</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
+          <t>https://www.indeed.com/viewjob?jk=f00372df43351c32</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
+          <t>https://www.indeed.com/viewjob?jk=c32309d8c8a7e9f5</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
+          <t>https://www.indeed.com/viewjob?jk=1457775431c42b5d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e18c32a05c4b7b4</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
+          <t>https://www.indeed.com/viewjob?jk=9e0cdecf9c920925</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
+          <t>https://www.indeed.com/viewjob?jk=27277386867af83d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=b68e13708328ab34</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
+          <t>https://www.indeed.com/viewjob?jk=98ec836b5a90abe7</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
+          <t>https://www.indeed.com/viewjob?jk=307ea8e3f4f1473f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9adba65ea4d57bea</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
+          <t>https://www.indeed.com/viewjob?jk=d529746fc7954941</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
+          <t>https://www.indeed.com/viewjob?jk=562632a0b3470f5e</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca5af3194895937a</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
+          <t>https://www.indeed.com/viewjob?jk=f12227fa17560e0f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3fc91f2cea0cff</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2fee489de51d1d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b42319358e9825d</t>
+          <t>https://www.indeed.com/viewjob?jk=152b4dc81897f107</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0828e77c3d7d3252</t>
+          <t>https://www.indeed.com/viewjob?jk=c481d564d5e78c78</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd855d8b7037bf65</t>
+          <t>https://www.indeed.com/viewjob?jk=118ac113f24389f4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=915279c42616c491</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c7864089908dfd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a05cfa47b40187d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, GCP, Hadoop, Scala, Snowflake, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d907377ff091f914</t>
+          <t>https://www.indeed.com/viewjob?jk=6c875e063114bb1c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Foley</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b9571cfd096f5e</t>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>AI Solution Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Agilify</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19f7de148c2aba2</t>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Network Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc1f317e66777dd</t>
+          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Solution Architect – Data Migration &amp; Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Kinesis, S3, RDS, Data Lake Storage, Medallion Architecture, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c20343bdf459df</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7b9a9c0a9082ee</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ea44a5cf8a55d70</t>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>API/Microservices/AWS Software Engineer - Remote</t>
+          <t>Security Data Analyst - Parsing</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8c4bfc649925e7</t>
+          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Foley</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Medallion Architecture, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, Azure, Event Hubs, BigQuery, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,102 +3471,102 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, Maven, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf7434fe21677c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Security Data Analyst - Parsing</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Databricks, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171de003fe5563fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Senior Software Engineer IV / V (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Auto.Live</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, Scala, Kafka, MySQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+          <t>https://www.indeed.com/viewjob?jk=42c2207352100be0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Sr. Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Engineer, Corp Solutions</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Papa John's</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Splunk, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,19 +3681,19 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb61fc433cd2352b</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Engineer, Corp Solutions</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Papa John's</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, CI/CD, Jenkins, Maven, Kubernetes, Jenkins, Git, Bitbucket</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlottesville, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Mass General Brigham</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+          <t>https://www.indeed.com/viewjob?jk=dccbfd697359c720</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Business Intelligence Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>American Red Cross</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Scala, DynamoDB, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Software Engineer- Greensboro, NC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Stake Center Locating</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Red Cross</t>
+          <t>Qureos</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b3d5c88d17dccb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Systems Engineer I</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Texas A&amp;M AgriLife Extension</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>College Station, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Data Modeling, dbt, Power BI, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+          <t>https://www.indeed.com/viewjob?jk=a99f136d94c9eab9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>Systems Engineer I</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Texas A&amp;M AgriLife Extension</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>College Station, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7956002449dfcaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=2b951b068dc32695</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3915e239710ba577</t>
+          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer- Greensboro, NC</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Stake Center Locating</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, ETL, ELT, Power BI, Git</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c8332d54e7fcd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf8e77549f4b069</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Database Developer (Contractor) - MNSITE-3762</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Qureos</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad6582003e647074</t>
+          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Systems Engineer I</t>
+          <t>Senior Software Engineer Backend Systems</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Texas A&amp;M AgriLife Extension</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a99f136d94c9eab9</t>
+          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Systems Engineer I</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Texas A&amp;M AgriLife Extension</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>College Station, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, RDS, Scala, Oracle, Jenkins, Terraform, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4275,181 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2b951b068dc32695</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Database Developer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Hollstadt Consulting</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>MN, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bdef6e08804da8cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Database Developer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>VIVA</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf8e77549f4b069</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Database Developer (Contractor) - MNSITE-3762</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>RE/SPEC Inc</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bac2143c91f124e3</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Backend Systems</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Health Data Analytics Institute</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Dedham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, ECS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Citizens</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Oracle, Jenkins, Terraform, Jenkins, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=69fdb765742c8dbb</t>
         </is>
